--- a/src/services/__fixtures__/plantilla-sucia.xlsx
+++ b/src/services/__fixtures__/plantilla-sucia.xlsx
@@ -1570,7 +1570,7 @@
     <row r="1">
       <c r="A1" s="46" t="inlineStr">
         <is>
-          <t>Validación</t>
+          <t>Validación2</t>
         </is>
       </c>
     </row>
